--- a/artfynd/A 40879-2025 artfynd.xlsx
+++ b/artfynd/A 40879-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96283156</v>
+        <v>96283197</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Nordlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Botrychium boreale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Milde</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strand (norra infarten) – Storån, Jmt</t>
+          <t>NA, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508229.3983514156</v>
+        <v>508267</v>
       </c>
       <c r="R2" t="n">
-        <v>7133708.110000939</v>
+        <v>7133612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,14 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>East allt</t>
+          <t>IS west</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,12 +788,7 @@
         <v>96283218</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508231.1316975669</v>
+        <v>508231</v>
       </c>
       <c r="R3" t="n">
-        <v>7133709.415630738</v>
+        <v>7133709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -925,50 +895,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96283135</v>
+        <v>96283156</v>
       </c>
       <c r="B4" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>221343</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NA, Jmt</t>
+          <t>Strand (norra infarten) – Storån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508249.4464222898</v>
+        <v>508229</v>
       </c>
       <c r="R4" t="n">
-        <v>7133680.409237836</v>
+        <v>7133708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +967,9 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1046,38 +1005,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96283216</v>
+        <v>96283201</v>
       </c>
       <c r="B5" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>222112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508274.3191044502</v>
+        <v>508266</v>
       </c>
       <c r="R5" t="n">
-        <v>7133634.940809642</v>
+        <v>7133617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,24 +1077,14 @@
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>IS east</t>
+          <t>Is west</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,6 +1108,328 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96283215</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508300</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7133555</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Is west</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96283135</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NA, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>508250</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7133681</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>East allt</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96283216</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strand (norra infarten) – Storån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>508274</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7133635</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>IS east</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 40879-2025 artfynd.xlsx
+++ b/artfynd/A 40879-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96283197</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96283218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96283156</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96283201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96283215</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96283135</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,8 +1469,22 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96283216</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>